--- a/2_clean/secondary_metrics.xlsx
+++ b/2_clean/secondary_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/swalshda_uvm_edu/Documents/Food Systems Research Center/Sustainability Metrics/Sustainability Metrics Manuscript/Metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="742" documentId="8_{735FDC36-AB7D-4B4C-AD9F-35DAC55E2D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C999FA10-89E2-4932-A0E4-1D856A1885B6}"/>
+  <xr:revisionPtr revIDLastSave="782" documentId="8_{735FDC36-AB7D-4B4C-AD9F-35DAC55E2D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1FB3D24-5454-4EF4-9B85-ECDDC8654666}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Economics" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Economics!$A$1:$Q$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Health!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Social!$A$1:$Q$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">utilities!$A$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">utilities!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="525">
   <si>
     <t>quality</t>
   </si>
@@ -887,9 +887,6 @@
     <t>populationAnnual</t>
   </si>
   <si>
-    <t>population5year</t>
-  </si>
-  <si>
     <t>ACS1, for non-census variables</t>
   </si>
   <si>
@@ -1289,9 +1286,6 @@
     <t>Model-based estimate for crude prevalence of lack of social and emotional support among adults. Question reads: How often do you get the social and emotional support that you need? (5-point Likert). Cutoff unclear?</t>
   </si>
   <si>
-    <t>1-year sample is done. Need to expand to all years</t>
-  </si>
-  <si>
     <t>firearmFatalities</t>
   </si>
   <si>
@@ -1620,6 +1614,15 @@
   </si>
   <si>
     <t>New question in 2024, only 1 year data</t>
+  </si>
+  <si>
+    <t>population5Year</t>
+  </si>
+  <si>
+    <t>population5YearSmooth</t>
+  </si>
+  <si>
+    <t>Population (5 year, smooth)</t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1940,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2070,29 +2073,20 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2101,6 +2095,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2606,11 +2606,11 @@
   <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.33203125" style="42" customWidth="1"/>
-    <col min="3" max="3" width="34.77734375" style="42" customWidth="1"/>
+    <col min="2" max="2" width="22" style="42" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" style="42" customWidth="1"/>
     <col min="4" max="5" width="8.109375" style="42" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
     <col min="8" max="8" width="39.77734375" customWidth="1"/>
     <col min="11" max="11" width="22.21875" customWidth="1"/>
     <col min="12" max="12" width="22.6640625" customWidth="1"/>
@@ -2632,19 +2632,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -2656,7 +2656,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -2675,120 +2675,132 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="24">
-        <v>3</v>
+      <c r="A2" s="23">
+        <v>2</v>
       </c>
       <c r="B2" s="59" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>458</v>
+        <v>13</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>420</v>
+        <v>14</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>419</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="H2" s="22"/>
       <c r="I2" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>304</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M2" s="22" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N2" s="22" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="O2" s="22"/>
       <c r="P2" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q2" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="24">
+        <v>3</v>
+      </c>
+      <c r="B3" s="59"/>
+      <c r="C3" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q3" s="22" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="35" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D4" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E4" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F4" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="20" t="s">
-        <v>450</v>
-      </c>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="24">
-        <v>3</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>457</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
       <c r="I4" s="34"/>
-      <c r="J4" s="45"/>
+      <c r="J4" s="34"/>
       <c r="K4" s="34"/>
       <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
+      <c r="M4" s="20"/>
       <c r="N4" s="34"/>
-      <c r="O4" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" s="34"/>
+      <c r="O4" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="P4" s="20"/>
       <c r="Q4" s="34" t="s">
         <v>32</v>
       </c>
@@ -2797,227 +2809,219 @@
       <c r="A5" s="24">
         <v>3</v>
       </c>
-      <c r="B5" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="60" t="s">
-        <v>449</v>
-      </c>
-      <c r="D5" s="53" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="24">
+        <v>3</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="60" t="s">
         <v>447</v>
       </c>
-      <c r="E5" s="53" t="s">
-        <v>447</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>455</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>418</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q5" s="22" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
-        <v>3</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="53" t="s">
-        <v>447</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>447</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="M6" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q6" s="22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="23">
-        <v>2</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>447</v>
+      <c r="D7" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>445</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>14</v>
+        <v>453</v>
       </c>
       <c r="G7" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="H7" s="22"/>
+      <c r="H7" s="22" t="s">
+        <v>416</v>
+      </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="22" t="s">
         <v>305</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="O7" s="22"/>
       <c r="P7" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>19</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="59" t="s">
+      <c r="A8" s="24">
+        <v>3</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" t="s">
+        <v>414</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q8" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="24">
+        <v>3</v>
+      </c>
+      <c r="B9" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>451</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="E8" s="35"/>
-      <c r="F8" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34" t="s">
-        <v>32</v>
+      <c r="C9" s="28" t="s">
+        <v>454</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>304</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="M9" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="N9" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q9" s="22" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="24">
         <v>3</v>
       </c>
-      <c r="B10" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="61" t="s">
+      <c r="B10" s="59"/>
+      <c r="C10" s="59" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="28" t="s">
@@ -3027,48 +3031,46 @@
         <v>94</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>453</v>
+        <v>37</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>248</v>
+        <v>327</v>
+      </c>
+      <c r="H10" t="s">
+        <v>450</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="K10" t="s">
+        <v>244</v>
       </c>
       <c r="L10" s="22" t="s">
         <v>316</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N10" s="22" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="O10" s="22"/>
       <c r="P10" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q10" s="22" t="s">
-        <v>249</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="24">
         <v>3</v>
       </c>
-      <c r="B11" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="61"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
       <c r="D11" s="28" t="s">
         <v>94</v>
       </c>
@@ -3076,13 +3078,13 @@
         <v>94</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H11" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>15</v>
@@ -3090,11 +3092,11 @@
       <c r="J11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K11" t="s">
-        <v>244</v>
+      <c r="K11" s="22" t="s">
+        <v>22</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M11" s="22" t="s">
         <v>17</v>
@@ -3107,17 +3109,15 @@
         <v>252</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>39</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="24">
         <v>3</v>
       </c>
-      <c r="B12" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="61"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="28" t="s">
         <v>94</v>
       </c>
@@ -3125,226 +3125,200 @@
         <v>94</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>36</v>
+        <v>451</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="H12" t="s">
-        <v>417</v>
+      <c r="H12" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="I12" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>22</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N12" s="22" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="O12" s="22"/>
       <c r="P12" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q12" s="22" t="s">
-        <v>385</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="24">
+      <c r="A13" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="24">
         <v>3</v>
       </c>
-      <c r="B13" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="28" t="s">
+      <c r="B14" s="59"/>
+      <c r="C14" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="F13" s="22" t="s">
+      <c r="D14" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="H14" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="G13" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>483</v>
-      </c>
-      <c r="I13" s="22" t="s">
+      <c r="I14" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K14" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="M13" s="22" t="s">
+      <c r="L14" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="M14" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="N13" s="22" t="s">
+      <c r="N14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="O13" s="22" t="s">
-        <v>503</v>
-      </c>
-      <c r="P13" s="22" t="s">
+      <c r="O14" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="P14" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="Q13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="33" t="s">
+      <c r="Q14" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="35" t="s">
+      <c r="B15" s="59"/>
+      <c r="C15" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="25" t="s">
+      <c r="D15" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34" t="s">
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34" t="s">
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
-        <v>3</v>
-      </c>
-      <c r="B15" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>454</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="N15" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q15" s="22" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="24">
         <v>3</v>
       </c>
-      <c r="B16" s="59" t="s">
-        <v>34</v>
-      </c>
+      <c r="B16" s="59"/>
       <c r="C16" s="28" t="s">
-        <v>456</v>
+        <v>43</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>339</v>
+        <v>452</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>340</v>
+        <v>267</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>305</v>
+        <v>16</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>22</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>341</v>
+        <v>44</v>
       </c>
       <c r="N16" s="22" t="s">
-        <v>342</v>
+        <v>45</v>
       </c>
       <c r="O16" s="22"/>
       <c r="P16" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>343</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3359,9 +3333,11 @@
     <sortCondition ref="F2:F16"/>
   </sortState>
   <dataConsolidate/>
-  <mergeCells count="2">
-    <mergeCell ref="C5:C6"/>
+  <mergeCells count="4">
     <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B2:B8"/>
+    <mergeCell ref="B9:B16"/>
+    <mergeCell ref="C7:C8"/>
   </mergeCells>
   <conditionalFormatting sqref="K4">
     <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
@@ -3403,19 +3379,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -3427,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -3449,23 +3425,23 @@
       <c r="A2" s="23">
         <v>2</v>
       </c>
-      <c r="B2" s="61" t="s">
-        <v>466</v>
-      </c>
-      <c r="C2" s="61" t="s">
+      <c r="B2" s="59" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" s="59" t="s">
         <v>50</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H2" t="s">
         <v>51</v>
@@ -3480,7 +3456,7 @@
         <v>244</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>52</v>
@@ -3502,19 +3478,19 @@
       <c r="A3" s="23">
         <v>2</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
       <c r="D3" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H3" t="s">
         <v>54</v>
@@ -3529,7 +3505,7 @@
         <v>244</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>52</v>
@@ -3548,19 +3524,19 @@
       <c r="A4" s="23">
         <v>2</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
       <c r="D4" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H4" t="s">
         <v>56</v>
@@ -3575,7 +3551,7 @@
         <v>244</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>52</v>
@@ -3597,15 +3573,15 @@
       <c r="A5" s="23">
         <v>2</v>
       </c>
-      <c r="B5" s="61"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="28" t="s">
         <v>258</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>261</v>
@@ -3614,7 +3590,7 @@
         <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>66</v>
@@ -3623,10 +3599,10 @@
         <v>272</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M5" s="22" t="s">
         <v>259</v>
@@ -3648,21 +3624,21 @@
       <c r="A6" s="23">
         <v>2</v>
       </c>
-      <c r="B6" s="61"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="28" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>269</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>270</v>
@@ -3674,10 +3650,10 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>17</v>
@@ -3695,26 +3671,26 @@
       <c r="A7" s="24">
         <v>3</v>
       </c>
-      <c r="B7" s="61" t="s">
-        <v>484</v>
-      </c>
-      <c r="C7" s="61" t="s">
+      <c r="B7" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="C7" s="59" t="s">
         <v>59</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G7" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H7" s="56" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
@@ -3723,47 +3699,47 @@
         <v>21</v>
       </c>
       <c r="K7" s="49" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P7" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="24">
         <v>3</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
       <c r="D8" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H8" s="56" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>15</v>
@@ -3772,49 +3748,49 @@
         <v>21</v>
       </c>
       <c r="K8" s="49" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P8" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="24">
         <v>3</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61" t="s">
+      <c r="B9" s="59"/>
+      <c r="C9" s="59" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>15</v>
@@ -3823,33 +3799,33 @@
         <v>21</v>
       </c>
       <c r="K9" s="49" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P9" s="50" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Q9" s="22" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="24">
         <v>3</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="28" t="s">
         <v>94</v>
       </c>
@@ -3857,33 +3833,33 @@
         <v>94</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H10" s="56" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J10" s="22" t="s">
         <v>21</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P10" s="49" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q10" s="22"/>
     </row>
@@ -3891,23 +3867,23 @@
       <c r="A11" s="26">
         <v>1</v>
       </c>
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="61" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>46</v>
@@ -3916,41 +3892,41 @@
         <v>94</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="O11" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="P11" s="22" t="s">
         <v>518</v>
-      </c>
-      <c r="P11" s="22" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
         <v>1</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
       <c r="D12" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I12" s="22" t="s">
         <v>46</v>
@@ -3959,22 +3935,22 @@
         <v>94</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="O12" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="P12" s="22" t="s">
         <v>518</v>
-      </c>
-      <c r="P12" s="22" t="s">
-        <v>520</v>
       </c>
       <c r="Q12" s="22"/>
     </row>
@@ -3982,21 +3958,21 @@
       <c r="A13" s="26">
         <v>1</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="61" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I13" t="s">
         <v>66</v>
@@ -4005,30 +3981,30 @@
         <v>94</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P13" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
         <v>1</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
       <c r="D14" s="29" t="s">
         <v>94</v>
       </c>
@@ -4043,7 +4019,7 @@
       <c r="L14" s="22"/>
       <c r="N14" s="46"/>
       <c r="O14" s="22" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="P14" s="22"/>
       <c r="Q14" s="22"/>
@@ -4052,21 +4028,21 @@
       <c r="A15" s="26">
         <v>1</v>
       </c>
-      <c r="B15" s="62"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="29" t="s">
         <v>97</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G15" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I15" t="s">
         <v>66</v>
@@ -4075,135 +4051,135 @@
         <v>94</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P15" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="24">
         <v>3</v>
       </c>
-      <c r="B16" s="61" t="s">
-        <v>338</v>
-      </c>
-      <c r="C16" s="61" t="s">
+      <c r="B16" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" s="59" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J16" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="M16" s="22" t="s">
         <v>323</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="M16" s="22" t="s">
-        <v>324</v>
       </c>
       <c r="N16" s="22"/>
       <c r="O16" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="P16" s="49" t="s">
-        <v>413</v>
+        <v>336</v>
+      </c>
+      <c r="P16" s="22" t="s">
+        <v>252</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="24">
         <v>3</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I17" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J17" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="M17" s="22" t="s">
         <v>323</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="M17" s="22" t="s">
-        <v>324</v>
       </c>
       <c r="N17" s="22"/>
       <c r="O17" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="P17" s="49" t="s">
-        <v>413</v>
+        <v>336</v>
+      </c>
+      <c r="P17" s="22" t="s">
+        <v>252</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="23">
         <v>2</v>
       </c>
-      <c r="B18" s="61"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="28" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>65</v>
@@ -4212,7 +4188,7 @@
         <v>120</v>
       </c>
       <c r="H18" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I18" s="22" t="s">
         <v>66</v>
@@ -4221,10 +4197,10 @@
         <v>21</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M18" s="22" t="s">
         <v>67</v>
@@ -4235,8 +4211,8 @@
       <c r="O18" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="P18" s="49" t="s">
-        <v>413</v>
+      <c r="P18" s="22" t="s">
+        <v>252</v>
       </c>
       <c r="Q18" s="22" t="s">
         <v>70</v>
@@ -4246,24 +4222,24 @@
       <c r="A19" s="23">
         <v>2</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="28" t="s">
         <v>71</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H19" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I19" s="22" t="s">
         <v>46</v>
@@ -4272,10 +4248,10 @@
         <v>21</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M19" s="22" t="s">
         <v>62</v>
@@ -4287,7 +4263,7 @@
         <v>73</v>
       </c>
       <c r="P19" s="22" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q19" s="22" t="s">
         <v>74</v>
@@ -4297,14 +4273,14 @@
       <c r="A20" s="26">
         <v>1</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="59" t="s">
         <v>76</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E20" s="28" t="s">
         <v>94</v>
@@ -4316,7 +4292,7 @@
         <v>120</v>
       </c>
       <c r="H20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>46</v>
@@ -4326,7 +4302,7 @@
       </c>
       <c r="K20" s="22"/>
       <c r="L20" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M20" s="22" t="s">
         <v>78</v>
@@ -4348,10 +4324,10 @@
       <c r="A21" s="26">
         <v>1</v>
       </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E21" s="28" t="s">
         <v>94</v>
@@ -4363,7 +4339,7 @@
         <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I21" s="22" t="s">
         <v>46</v>
@@ -4373,7 +4349,7 @@
       </c>
       <c r="K21" s="22"/>
       <c r="L21" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M21" s="22" t="s">
         <v>78</v>
@@ -4395,36 +4371,36 @@
       <c r="A22" s="23">
         <v>2</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61" t="s">
+      <c r="B22" s="59"/>
+      <c r="C22" s="59" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G22" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H22" t="s">
+        <v>344</v>
+      </c>
+      <c r="I22" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="I22" s="22" t="s">
+      <c r="J22" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="J22" s="22" t="s">
-        <v>347</v>
-      </c>
       <c r="K22" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M22" s="22" t="s">
         <v>85</v>
@@ -4434,23 +4410,23 @@
       </c>
       <c r="O22" s="22"/>
       <c r="P22" s="50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q22" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="23">
         <v>2</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>87</v>
@@ -4459,7 +4435,7 @@
         <v>120</v>
       </c>
       <c r="H23" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I23" s="22" t="s">
         <v>15</v>
@@ -4468,10 +4444,10 @@
         <v>88</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M23" s="22" t="s">
         <v>89</v>
@@ -4540,7 +4516,8 @@
     <col min="6" max="6" width="34.21875" customWidth="1"/>
     <col min="7" max="7" width="17.5546875" customWidth="1"/>
     <col min="8" max="8" width="28.77734375" customWidth="1"/>
-    <col min="11" max="12" width="14.21875" customWidth="1"/>
+    <col min="11" max="11" width="26.21875" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" customWidth="1"/>
     <col min="15" max="15" width="35" customWidth="1"/>
     <col min="16" max="16" width="25.109375" customWidth="1"/>
     <col min="17" max="17" width="28.33203125" customWidth="1"/>
@@ -4557,19 +4534,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -4581,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -4610,19 +4587,19 @@
         <v>99</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I2" s="22" t="s">
         <v>15</v>
@@ -4631,10 +4608,10 @@
         <v>16</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>311</v>
+        <v>524</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>100</v>
@@ -4647,24 +4624,24 @@
         <v>252</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="23">
         <v>2</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>102</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>103</v>
@@ -4683,7 +4660,7 @@
         <v>247</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>105</v>
@@ -4705,15 +4682,15 @@
       <c r="A4" s="24">
         <v>3</v>
       </c>
-      <c r="B4" s="61"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="28" t="s">
         <v>109</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>110</v>
@@ -4722,7 +4699,7 @@
         <v>120</v>
       </c>
       <c r="H4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>15</v>
@@ -4731,10 +4708,10 @@
         <v>21</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>23</v>
@@ -4743,10 +4720,10 @@
         <v>24</v>
       </c>
       <c r="O4" s="22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P4" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q4" s="22" t="s">
         <v>112</v>
@@ -4756,15 +4733,15 @@
       <c r="A5" s="24">
         <v>3</v>
       </c>
-      <c r="B5" s="61"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="38" t="s">
         <v>113</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>114</v>
@@ -4773,7 +4750,7 @@
         <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>15</v>
@@ -4782,10 +4759,10 @@
         <v>21</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M5" s="22" t="s">
         <v>115</v>
@@ -4798,19 +4775,19 @@
         <v>252</v>
       </c>
       <c r="Q5" s="22" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="61"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="39" t="s">
         <v>117</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="40" t="s">
@@ -4836,15 +4813,15 @@
       <c r="A7" s="24">
         <v>3</v>
       </c>
-      <c r="B7" s="61"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="47" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>119</v>
@@ -4853,7 +4830,7 @@
         <v>120</v>
       </c>
       <c r="H7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
@@ -4862,10 +4839,10 @@
         <v>21</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>121</v>
@@ -4880,33 +4857,33 @@
         <v>252</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="23">
         <v>2</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="59" t="s">
         <v>125</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
@@ -4915,37 +4892,37 @@
         <v>94</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M8" t="s">
+        <v>401</v>
+      </c>
+      <c r="N8" t="s">
         <v>402</v>
       </c>
-      <c r="N8" t="s">
-        <v>403</v>
-      </c>
       <c r="O8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P8" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="61"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="39" t="s">
         <v>124</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="40" t="s">
@@ -4969,15 +4946,15 @@
       <c r="A10" s="23">
         <v>2</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="29" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>126</v>
@@ -4986,7 +4963,7 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>15</v>
@@ -4995,10 +4972,10 @@
         <v>21</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M10" s="22" t="s">
         <v>23</v>
@@ -5020,17 +4997,17 @@
       <c r="A11" s="24">
         <v>3</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="59" t="s">
         <v>129</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>130</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>131</v>
@@ -5039,7 +5016,7 @@
         <v>120</v>
       </c>
       <c r="H11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>15</v>
@@ -5048,10 +5025,10 @@
         <v>21</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M11" s="22" t="s">
         <v>23</v>
@@ -5070,15 +5047,15 @@
       <c r="A12" s="23">
         <v>2</v>
       </c>
-      <c r="B12" s="61"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="28" t="s">
         <v>133</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>134</v>
@@ -5087,7 +5064,7 @@
         <v>120</v>
       </c>
       <c r="H12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I12" s="22" t="s">
         <v>15</v>
@@ -5096,10 +5073,10 @@
         <v>16</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M12" s="22" t="s">
         <v>100</v>
@@ -5121,15 +5098,15 @@
       <c r="A13" s="23">
         <v>2</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="62" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="61" t="s">
         <v>137</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>138</v>
@@ -5138,7 +5115,7 @@
         <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I13" s="22" t="s">
         <v>15</v>
@@ -5147,10 +5124,10 @@
         <v>21</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M13" s="22" t="s">
         <v>23</v>
@@ -5172,22 +5149,22 @@
       <c r="A14" s="23">
         <v>2</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="62"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="61"/>
       <c r="D14" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I14" s="22" t="s">
         <v>15</v>
@@ -5196,49 +5173,49 @@
         <v>94</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M14" t="s">
+        <v>401</v>
+      </c>
+      <c r="N14" t="s">
         <v>402</v>
       </c>
-      <c r="N14" t="s">
-        <v>403</v>
-      </c>
       <c r="O14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P14" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="23">
         <v>2</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61" t="s">
+      <c r="B15" s="59"/>
+      <c r="C15" s="59" t="s">
         <v>140</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G15" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I15" s="22" t="s">
         <v>46</v>
@@ -5247,45 +5224,45 @@
         <v>21</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M15" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="N15" s="22" t="s">
         <v>394</v>
-      </c>
-      <c r="N15" s="22" t="s">
-        <v>395</v>
       </c>
       <c r="O15" s="22"/>
       <c r="P15" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="23">
         <v>2</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G16" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>46</v>
@@ -5294,47 +5271,47 @@
         <v>21</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M16" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="N16" s="22" t="s">
         <v>394</v>
-      </c>
-      <c r="N16" s="22" t="s">
-        <v>395</v>
       </c>
       <c r="O16" s="22"/>
       <c r="P16" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="24">
         <v>3</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="62" t="s">
-        <v>467</v>
+      <c r="B17" s="59"/>
+      <c r="C17" s="61" t="s">
+        <v>465</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G17" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H17" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I17" s="22" t="s">
         <v>15</v>
@@ -5343,10 +5320,10 @@
         <v>21</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M17" s="22" t="s">
         <v>23</v>
@@ -5358,29 +5335,29 @@
         <v>255</v>
       </c>
       <c r="Q17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="24">
         <v>3</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G18" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I18" s="22" t="s">
         <v>15</v>
@@ -5389,22 +5366,22 @@
         <v>94</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M18" t="s">
+        <v>401</v>
+      </c>
+      <c r="N18" t="s">
         <v>402</v>
-      </c>
-      <c r="N18" t="s">
-        <v>403</v>
       </c>
       <c r="P18" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q18" s="22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5450,7 +5427,7 @@
     <col min="5" max="5" width="9.6640625" style="29" customWidth="1"/>
     <col min="6" max="6" width="33.6640625" customWidth="1"/>
     <col min="7" max="7" width="17.44140625" customWidth="1"/>
-    <col min="8" max="8" width="54" customWidth="1"/>
+    <col min="8" max="8" width="39.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" customWidth="1"/>
     <col min="11" max="11" width="21.33203125" customWidth="1"/>
@@ -5473,19 +5450,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -5497,7 +5474,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -5526,19 +5503,19 @@
         <v>142</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I2" s="22" t="s">
         <v>46</v>
@@ -5550,7 +5527,7 @@
         <v>244</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>143</v>
@@ -5577,19 +5554,19 @@
         <v>147</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>46</v>
@@ -5601,7 +5578,7 @@
         <v>244</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>148</v>
@@ -5630,19 +5607,19 @@
         <v>152</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>15</v>
@@ -5651,10 +5628,10 @@
         <v>16</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>44</v>
@@ -5667,7 +5644,7 @@
         <v>252</v>
       </c>
       <c r="Q4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -5678,22 +5655,22 @@
         <v>153</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>154</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>66</v>
@@ -5702,10 +5679,10 @@
         <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M5" s="22" t="s">
         <v>155</v>
@@ -5725,26 +5702,26 @@
       <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="59" t="s">
         <v>158</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>160</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I6" s="30" t="s">
         <v>15</v>
@@ -5756,7 +5733,7 @@
         <v>244</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>17</v>
@@ -5776,24 +5753,24 @@
       <c r="A7" s="23">
         <v>2</v>
       </c>
-      <c r="B7" s="61"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="28" t="s">
         <v>159</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
@@ -5802,10 +5779,10 @@
         <v>16</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>44</v>
@@ -5814,13 +5791,13 @@
         <v>45</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P7" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R7"/>
     </row>
@@ -5835,19 +5812,19 @@
         <v>163</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>164</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>15</v>
@@ -5856,10 +5833,10 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M8" s="22" t="s">
         <v>17</v>
@@ -5868,13 +5845,13 @@
         <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P8" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -5886,19 +5863,19 @@
         <v>165</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>46</v>
@@ -5910,7 +5887,7 @@
         <v>244</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M9" s="22" t="s">
         <v>17</v>
@@ -5919,13 +5896,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P9" s="22" t="s">
         <v>252</v>
       </c>
       <c r="Q9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -5935,7 +5912,7 @@
         <v>166</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="34" t="s">
@@ -5962,19 +5939,19 @@
         <v>168</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>15</v>
@@ -5986,7 +5963,7 @@
         <v>244</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M11" s="22" t="s">
         <v>44</v>
@@ -5999,7 +5976,7 @@
         <v>252</v>
       </c>
       <c r="Q11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -6007,23 +5984,23 @@
         <v>2</v>
       </c>
       <c r="B12" s="60"/>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="59" t="s">
         <v>169</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I12" s="22" t="s">
         <v>46</v>
@@ -6035,20 +6012,20 @@
         <v>244</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N12" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O12" s="22"/>
       <c r="P12" s="49" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -6056,21 +6033,21 @@
         <v>2</v>
       </c>
       <c r="B13" s="60"/>
-      <c r="C13" s="61"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I13" s="22" t="s">
         <v>46</v>
@@ -6082,7 +6059,7 @@
         <v>244</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M13" s="22" t="s">
         <v>44</v>
@@ -6092,10 +6069,10 @@
       </c>
       <c r="O13" s="22"/>
       <c r="P13" s="49" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -6103,21 +6080,21 @@
         <v>2</v>
       </c>
       <c r="B14" s="60"/>
-      <c r="C14" s="61"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I14" s="22" t="s">
         <v>46</v>
@@ -6129,20 +6106,20 @@
         <v>244</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N14" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O14" s="22"/>
       <c r="P14" s="49" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -6156,7 +6133,7 @@
         <v>171</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="44" t="s">
@@ -6244,19 +6221,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I1" s="17" t="s">
         <v>5</v>
@@ -6268,7 +6245,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M1" s="17" t="s">
         <v>8</v>
@@ -6290,14 +6267,14 @@
       <c r="A2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="61" t="s">
         <v>173</v>
       </c>
       <c r="C2" s="37" t="s">
         <v>174</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E2" s="37"/>
       <c r="F2" s="20" t="s">
@@ -6319,12 +6296,12 @@
       <c r="A3" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62"/>
+      <c r="B3" s="61"/>
       <c r="C3" s="37" t="s">
         <v>175</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E3" s="37"/>
       <c r="F3" s="20" t="s">
@@ -6346,12 +6323,12 @@
       <c r="A4" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="62"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="37" t="s">
         <v>176</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E4" s="37"/>
       <c r="F4" s="20" t="s">
@@ -6373,12 +6350,12 @@
       <c r="A5" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="62"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="37" t="s">
         <v>177</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="20" t="s">
@@ -6400,24 +6377,24 @@
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="62"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="29" t="s">
         <v>178</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G6" t="s">
         <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
@@ -6426,37 +6403,37 @@
         <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M6" t="s">
+        <v>401</v>
+      </c>
+      <c r="N6" t="s">
         <v>402</v>
       </c>
-      <c r="N6" t="s">
-        <v>403</v>
-      </c>
       <c r="O6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P6" t="s">
         <v>252</v>
       </c>
       <c r="Q6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="62"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="37" t="s">
         <v>179</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E7" s="37"/>
       <c r="F7" t="s">
@@ -6478,12 +6455,12 @@
       <c r="A8" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="62"/>
+      <c r="B8" s="61"/>
       <c r="C8" s="37" t="s">
         <v>180</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E8" s="37"/>
       <c r="F8" t="s">
@@ -6505,26 +6482,26 @@
       <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="61" t="s">
         <v>181</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>182</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F9" t="s">
+        <v>370</v>
+      </c>
+      <c r="G9" t="s">
+        <v>327</v>
+      </c>
+      <c r="H9" t="s">
         <v>371</v>
-      </c>
-      <c r="G9" t="s">
-        <v>328</v>
-      </c>
-      <c r="H9" t="s">
-        <v>372</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -6536,7 +6513,7 @@
         <v>243</v>
       </c>
       <c r="L9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M9" t="s">
         <v>17</v>
@@ -6545,32 +6522,32 @@
         <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P9" t="s">
         <v>252</v>
       </c>
       <c r="Q9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" s="62"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="29" t="s">
         <v>183</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" t="s">
         <v>184</v>
       </c>
       <c r="G10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H10" t="s">
         <v>184</v>
@@ -6585,7 +6562,7 @@
         <v>243</v>
       </c>
       <c r="L10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M10" t="s">
         <v>17</v>
@@ -6605,22 +6582,22 @@
       <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="62"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="29" t="s">
         <v>186</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" t="s">
         <v>187</v>
       </c>
       <c r="G11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H11" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -6632,7 +6609,7 @@
         <v>243</v>
       </c>
       <c r="L11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M11" t="s">
         <v>17</v>
@@ -6652,12 +6629,12 @@
       <c r="A12" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="62"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="37" t="s">
         <v>189</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E12" s="37"/>
       <c r="F12" t="s">
@@ -6672,7 +6649,7 @@
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
       <c r="O12" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P12" s="20"/>
       <c r="Q12" s="20"/>
@@ -6681,10 +6658,10 @@
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="61" t="s">
         <v>201</v>
       </c>
       <c r="D13" s="29" t="s">
@@ -6694,13 +6671,13 @@
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G13" t="s">
         <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -6709,10 +6686,10 @@
         <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
@@ -6725,13 +6702,13 @@
         <v>252</v>
       </c>
       <c r="Q13" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
       <c r="D14" s="29" t="s">
         <v>94</v>
       </c>
@@ -6739,7 +6716,7 @@
         <v>94</v>
       </c>
       <c r="F14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G14" t="s">
         <v>120</v>
@@ -6753,7 +6730,7 @@
       <c r="N14"/>
       <c r="O14"/>
       <c r="P14" s="48" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q14"/>
     </row>
@@ -6761,15 +6738,15 @@
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="62"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="29" t="s">
         <v>196</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F15" t="s">
         <v>197</v>
@@ -6778,7 +6755,7 @@
         <v>120</v>
       </c>
       <c r="H15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
@@ -6787,10 +6764,10 @@
         <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M15" t="s">
         <v>23</v>
@@ -6810,12 +6787,12 @@
       <c r="A16" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="62"/>
+      <c r="B16" s="61"/>
       <c r="C16" s="37" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="20" t="s">
@@ -6839,12 +6816,12 @@
       <c r="A17" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="62"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="37" t="s">
         <v>200</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E17" s="37"/>
       <c r="F17" s="20" t="s">
@@ -6868,14 +6845,14 @@
       <c r="A18" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="61" t="s">
         <v>202</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>203</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="20" t="s">
@@ -6897,12 +6874,12 @@
       <c r="A19" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="62"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="37" t="s">
         <v>204</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E19" s="37"/>
       <c r="F19" t="s">
@@ -6920,7 +6897,7 @@
         <v>205</v>
       </c>
       <c r="P19" s="57" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Q19" s="20"/>
     </row>
@@ -6928,15 +6905,15 @@
       <c r="A20" s="20">
         <v>2</v>
       </c>
-      <c r="B20" s="62"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="29" t="s">
         <v>206</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F20" t="s">
         <v>207</v>
@@ -6952,10 +6929,10 @@
         <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="L20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M20" t="s">
         <v>26</v>
@@ -6975,23 +6952,23 @@
       <c r="A21">
         <v>2</v>
       </c>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="61" t="s">
         <v>190</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>191</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F21" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H21" t="s">
         <v>192</v>
@@ -7003,10 +6980,10 @@
         <v>16</v>
       </c>
       <c r="K21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M21" t="s">
         <v>17</v>
@@ -7026,12 +7003,12 @@
       <c r="A22">
         <v>2</v>
       </c>
-      <c r="B22" s="62"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="37" t="s">
         <v>194</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E22" s="37"/>
       <c r="F22" s="19" t="s">
@@ -7046,7 +7023,7 @@
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
       <c r="O22" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
@@ -7086,7 +7063,7 @@
       <formula>"rework"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A11 A13:A15 A18 A21:A22 A6">
+  <conditionalFormatting sqref="A6 A9:A11 A13:A15 A18 A21:A22">
     <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
       <formula>3</formula>
     </cfRule>
@@ -7097,7 +7074,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6 K10:L11 F10:H22 L15 Q15:Q17 I20 Q20:Q22 F1:H8 Q2:Q13 I6:J6">
+  <conditionalFormatting sqref="F1:H8 Q2:Q13 I6:J6 L6 K10:L11 F10:H22 L15 Q15:Q17 I20 Q20:Q22">
     <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
       <formula>"NONE"</formula>
     </cfRule>
@@ -7107,7 +7084,7 @@
       <formula>"NONE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:L13">
+  <conditionalFormatting sqref="L13">
     <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"NONE"</formula>
     </cfRule>
@@ -7131,80 +7108,80 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="72" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="66"/>
+      <c r="B2" s="73"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="B3" s="68"/>
+      <c r="B3" s="63"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="62" t="s">
         <v>213</v>
       </c>
-      <c r="B5" s="68"/>
+      <c r="B5" s="63"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="B6" s="64"/>
+      <c r="B6" s="67"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="63"/>
-      <c r="B7" s="64"/>
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="68"/>
+      <c r="B8" s="63"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="66" t="s">
         <v>216</v>
       </c>
-      <c r="B9" s="64"/>
+      <c r="B9" s="67"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
     </row>
     <row r="11" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="72"/>
+      <c r="B11" s="69"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="70" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="68"/>
+      <c r="B12" s="63"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="74"/>
-      <c r="B13" s="68"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="63"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="B14" s="68"/>
+      <c r="B14" s="63"/>
     </row>
     <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="B15" s="70"/>
+      <c r="B15" s="65"/>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
@@ -7230,18 +7207,18 @@
     </row>
     <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -7286,10 +7263,10 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -7373,6 +7350,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A8:B8"/>
@@ -7381,12 +7364,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A9" r:id="rId1" xr:uid="{A59DB292-A126-46C8-AAB0-2FF5AD1DDD57}"/>
@@ -7400,7 +7377,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E65C56-A834-4ED4-A193-64A017DCA518}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -7448,7 +7425,7 @@
         <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C2" t="s">
         <v>38</v>
@@ -7520,10 +7497,10 @@
         <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -7543,7 +7520,7 @@
         <v>252</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
         <v>278</v>
@@ -7555,10 +7532,10 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -7566,10 +7543,10 @@
         <v>252</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>522</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -7578,30 +7555,33 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
+        <v>280</v>
+      </c>
+      <c r="H7" t="s">
         <v>281</v>
       </c>
-      <c r="H7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>252</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>524</v>
       </c>
       <c r="C8" t="s">
-        <v>284</v>
+        <v>523</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>285</v>
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>280</v>
       </c>
       <c r="H8" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7609,19 +7589,19 @@
         <v>252</v>
       </c>
       <c r="B9" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="C9" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" t="s">
+        <v>284</v>
+      </c>
+      <c r="H9" t="s">
         <v>285</v>
-      </c>
-      <c r="E9" t="s">
-        <v>285</v>
-      </c>
-      <c r="H9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7629,22 +7609,19 @@
         <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>306</v>
       </c>
       <c r="C10" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>284</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="H10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7652,22 +7629,22 @@
         <v>252</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="H11" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7675,25 +7652,22 @@
         <v>252</v>
       </c>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" t="s">
-        <v>18</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7701,10 +7675,10 @@
         <v>252</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C13" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -7713,7 +7687,7 @@
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -7727,10 +7701,10 @@
         <v>252</v>
       </c>
       <c r="B14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -7739,7 +7713,7 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -7753,10 +7727,10 @@
         <v>252</v>
       </c>
       <c r="B15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -7765,7 +7739,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -7779,16 +7753,19 @@
         <v>252</v>
       </c>
       <c r="B16" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>298</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -7802,10 +7779,10 @@
         <v>252</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C17" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -7825,45 +7802,68 @@
         <v>252</v>
       </c>
       <c r="B18" t="s">
-        <v>501</v>
+        <v>313</v>
       </c>
       <c r="C18" t="s">
-        <v>500</v>
-      </c>
-      <c r="F18" t="s">
-        <v>502</v>
+        <v>312</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="B19" t="s">
-        <v>355</v>
+        <v>499</v>
+      </c>
+      <c r="C19" t="s">
+        <v>498</v>
       </c>
       <c r="F19" t="s">
-        <v>356</v>
-      </c>
-      <c r="G19" t="s">
-        <v>357</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B20" t="s">
+        <v>354</v>
+      </c>
+      <c r="F20" t="s">
+        <v>355</v>
+      </c>
+      <c r="G20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" t="s">
         <v>247</v>
       </c>
-      <c r="F20" t="s">
-        <v>303</v>
-      </c>
-      <c r="G20" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.4" x14ac:dyDescent="0.3"/>
+      <c r="F21" t="s">
+        <v>302</v>
+      </c>
+      <c r="G21" t="s">
+        <v>357</v>
+      </c>
+    </row>
     <row r="26" spans="1:9" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:I7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">

--- a/2_clean/secondary_metrics.xlsx
+++ b/2_clean/secondary_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/swalshda_uvm_edu/Documents/Food Systems Research Center/Sustainability Metrics/Sustainability Metrics Manuscript/Metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="782" documentId="8_{735FDC36-AB7D-4B4C-AD9F-35DAC55E2D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1FB3D24-5454-4EF4-9B85-ECDDC8654666}"/>
+  <xr:revisionPtr revIDLastSave="810" documentId="8_{735FDC36-AB7D-4B4C-AD9F-35DAC55E2D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA75AC61-8320-488A-B6ED-F0ECA468D5F5}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Economics" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Economics!$A$1:$Q$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Health!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Social!$A$1:$Q$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">utilities!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">utilities!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="523">
   <si>
     <t>quality</t>
   </si>
@@ -551,9 +551,6 @@
     <t>total quantity non-food ag products</t>
   </si>
   <si>
-    <t>NASS might have this, but I'm not sure it is split out in this particular way.</t>
-  </si>
-  <si>
     <t>value added market</t>
   </si>
   <si>
@@ -671,9 +668,6 @@
     <t>outmigration</t>
   </si>
   <si>
-    <t>Annual population change (%)</t>
-  </si>
-  <si>
     <t>Have the data here, need to rework variable though</t>
   </si>
   <si>
@@ -821,9 +815,6 @@
     <t>done unless we want source instead of UW</t>
   </si>
   <si>
-    <t>to do - calculate from census</t>
-  </si>
-  <si>
     <t>carbon stocks</t>
   </si>
   <si>
@@ -1424,18 +1415,6 @@
     <t>Standard deviation of distribution of tree sizes as measured by DBH (diameter at breast height)</t>
   </si>
   <si>
-    <t>NDVI</t>
-  </si>
-  <si>
-    <t>Annualized NDVI (normalized difference vegetation index)</t>
-  </si>
-  <si>
-    <t>depends</t>
-  </si>
-  <si>
-    <t>Acres of forest</t>
-  </si>
-  <si>
     <t>U.S. Forest Service, Forest Inventory Analysis (2025)</t>
   </si>
   <si>
@@ -1523,9 +1502,6 @@
     <t>propInvasive</t>
   </si>
   <si>
-    <t>maybe?</t>
-  </si>
-  <si>
     <t xml:space="preserve">done, not sure whether this is best way to handle it though. </t>
   </si>
   <si>
@@ -1623,6 +1599,24 @@
   </si>
   <si>
     <t>Population (5 year, smooth)</t>
+  </si>
+  <si>
+    <t>Acres operated, smooth</t>
+  </si>
+  <si>
+    <t>acresOperatedSmooth</t>
+  </si>
+  <si>
+    <t>2 years</t>
+  </si>
+  <si>
+    <t>Annual population change</t>
+  </si>
+  <si>
+    <t>populationChangePerc</t>
+  </si>
+  <si>
+    <t>Need to see whether state or county level makes more sense based on number of observations. Also note that 2024 data exist but are very sparse (about a third of the observations of 2021). Consider NDVI as an alternative?</t>
   </si>
 </sst>
 </file>
@@ -2632,19 +2626,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -2656,7 +2650,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -2685,16 +2679,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H2" s="22"/>
       <c r="I2" s="22" t="s">
@@ -2704,10 +2698,10 @@
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>17</v>
@@ -2717,7 +2711,7 @@
       </c>
       <c r="O2" s="22"/>
       <c r="P2" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q2" s="22" t="s">
         <v>19</v>
@@ -2729,22 +2723,22 @@
       </c>
       <c r="B3" s="59"/>
       <c r="C3" s="28" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>15</v>
@@ -2756,7 +2750,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>30</v>
@@ -2766,10 +2760,10 @@
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q3" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -2798,7 +2792,7 @@
       <c r="M4" s="20"/>
       <c r="N4" s="34"/>
       <c r="O4" s="20" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="P4" s="20"/>
       <c r="Q4" s="34" t="s">
@@ -2811,10 +2805,10 @@
       </c>
       <c r="B5" s="59"/>
       <c r="C5" s="35" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E5" s="35"/>
       <c r="F5" s="34" t="s">
@@ -2845,7 +2839,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="40" t="s">
@@ -2873,22 +2867,22 @@
       </c>
       <c r="B7" s="59"/>
       <c r="C7" s="60" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
@@ -2897,10 +2891,10 @@
         <v>21</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>30</v>
@@ -2910,10 +2904,10 @@
       </c>
       <c r="O7" s="22"/>
       <c r="P7" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -2923,10 +2917,10 @@
       <c r="B8" s="59"/>
       <c r="C8" s="60"/>
       <c r="D8" s="53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>25</v>
@@ -2935,7 +2929,7 @@
         <v>120</v>
       </c>
       <c r="H8" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>15</v>
@@ -2944,10 +2938,10 @@
         <v>16</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M8" s="22" t="s">
         <v>26</v>
@@ -2959,7 +2953,7 @@
         <v>28</v>
       </c>
       <c r="P8" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q8" s="22" t="s">
         <v>29</v>
@@ -2973,22 +2967,22 @@
         <v>34</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>15</v>
@@ -2997,23 +2991,23 @@
         <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q9" s="22" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -3034,10 +3028,10 @@
         <v>37</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H10" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>15</v>
@@ -3046,10 +3040,10 @@
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M10" s="22" t="s">
         <v>17</v>
@@ -3059,7 +3053,7 @@
       </c>
       <c r="O10" s="22"/>
       <c r="P10" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q10" s="22" t="s">
         <v>39</v>
@@ -3081,10 +3075,10 @@
         <v>36</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H11" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>15</v>
@@ -3096,7 +3090,7 @@
         <v>22</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M11" s="22" t="s">
         <v>17</v>
@@ -3106,10 +3100,10 @@
       </c>
       <c r="O11" s="22"/>
       <c r="P11" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -3125,13 +3119,13 @@
         <v>94</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I12" s="22" t="s">
         <v>15</v>
@@ -3143,7 +3137,7 @@
         <v>22</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M12" s="22" t="s">
         <v>30</v>
@@ -3153,10 +3147,10 @@
       </c>
       <c r="O12" s="22"/>
       <c r="P12" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q12" s="22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -3165,10 +3159,10 @@
       </c>
       <c r="B13" s="59"/>
       <c r="C13" s="35" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E13" s="35"/>
       <c r="F13" s="40" t="s">
@@ -3199,19 +3193,19 @@
         <v>40</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="I14" s="22" t="s">
         <v>15</v>
@@ -3223,7 +3217,7 @@
         <v>22</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M14" s="22" t="s">
         <v>17</v>
@@ -3232,13 +3226,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="P14" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q14" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -3250,7 +3244,7 @@
         <v>42</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="25" t="s">
@@ -3281,19 +3275,19 @@
         <v>43</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>15</v>
@@ -3305,7 +3299,7 @@
         <v>22</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M16" s="22" t="s">
         <v>44</v>
@@ -3315,10 +3309,10 @@
       </c>
       <c r="O16" s="22"/>
       <c r="P16" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3351,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802AE4B4-391E-474A-9621-08E11B188749}">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.109375" style="51" customWidth="1"/>
@@ -3379,19 +3373,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -3403,7 +3397,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -3426,22 +3420,22 @@
         <v>2</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C2" s="59" t="s">
         <v>50</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
         <v>51</v>
@@ -3453,22 +3447,22 @@
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>52</v>
       </c>
       <c r="N2" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="P2" t="s">
         <v>251</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="P2" t="s">
-        <v>253</v>
       </c>
       <c r="Q2" s="22" t="s">
         <v>53</v>
@@ -3481,16 +3475,16 @@
       <c r="B3" s="59"/>
       <c r="C3" s="59"/>
       <c r="D3" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H3" t="s">
         <v>54</v>
@@ -3502,19 +3496,19 @@
         <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>52</v>
       </c>
       <c r="N3" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="P3" t="s">
         <v>251</v>
-      </c>
-      <c r="P3" t="s">
-        <v>253</v>
       </c>
       <c r="Q3" s="22" t="s">
         <v>55</v>
@@ -3527,16 +3521,16 @@
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
       <c r="D4" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H4" t="s">
         <v>56</v>
@@ -3548,22 +3542,22 @@
         <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>52</v>
       </c>
       <c r="N4" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="O4" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="P4" t="s">
         <v>251</v>
-      </c>
-      <c r="O4" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="P4" t="s">
-        <v>253</v>
       </c>
       <c r="Q4" s="22" t="s">
         <v>57</v>
@@ -3575,49 +3569,49 @@
       </c>
       <c r="B5" s="59"/>
       <c r="C5" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>258</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>261</v>
       </c>
       <c r="G5" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>66</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M5" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="N5" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="P5" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q5" s="22" t="s">
         <v>259</v>
-      </c>
-      <c r="N5" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="O5" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="P5" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q5" s="22" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -3629,19 +3623,19 @@
         <v>58</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I6" s="22" t="s">
         <v>15</v>
@@ -3650,10 +3644,10 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>17</v>
@@ -3661,10 +3655,10 @@
       <c r="N6" s="22"/>
       <c r="O6" s="22"/>
       <c r="P6" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -3672,25 +3666,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C7" s="59" t="s">
         <v>59</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="G7" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H7" s="56" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
@@ -3699,25 +3693,25 @@
         <v>21</v>
       </c>
       <c r="K7" s="49" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="P7" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -3727,19 +3721,19 @@
       <c r="B8" s="59"/>
       <c r="C8" s="59"/>
       <c r="D8" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H8" s="56" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>15</v>
@@ -3748,25 +3742,25 @@
         <v>21</v>
       </c>
       <c r="K8" s="49" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="P8" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -3774,23 +3768,23 @@
         <v>3</v>
       </c>
       <c r="B9" s="59"/>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="28" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>15</v>
@@ -3799,91 +3793,91 @@
         <v>21</v>
       </c>
       <c r="K9" s="49" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="P9" s="50" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="Q9" s="22" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
-        <v>3</v>
-      </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="28" t="s">
+      <c r="A10" s="26">
+        <v>1</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="F10" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="H10" s="56" t="s">
-        <v>459</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>460</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>21</v>
-      </c>
       <c r="K10" s="22" t="s">
-        <v>461</v>
+        <v>279</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
+        <v>312</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="N10" s="46" t="s">
+        <v>500</v>
+      </c>
       <c r="O10" s="22" t="s">
-        <v>519</v>
-      </c>
-      <c r="P10" s="49" t="s">
-        <v>491</v>
-      </c>
-      <c r="Q10" s="22"/>
+        <v>508</v>
+      </c>
+      <c r="P10" s="22" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
         <v>1</v>
       </c>
-      <c r="B11" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>93</v>
-      </c>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
       <c r="D11" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>46</v>
@@ -3892,279 +3886,285 @@
         <v>94</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="N11" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="O11" s="22" t="s">
         <v>508</v>
       </c>
-      <c r="O11" s="22" t="s">
-        <v>516</v>
-      </c>
       <c r="P11" s="22" t="s">
-        <v>518</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="Q11" s="22"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
         <v>1</v>
       </c>
       <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
+      <c r="C12" s="61" t="s">
+        <v>95</v>
+      </c>
       <c r="D12" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>328</v>
+        <v>120</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>515</v>
-      </c>
-      <c r="I12" s="22" t="s">
-        <v>46</v>
+        <v>506</v>
+      </c>
+      <c r="I12" t="s">
+        <v>66</v>
       </c>
       <c r="J12" s="22" t="s">
         <v>94</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>507</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>508</v>
-      </c>
-      <c r="O12" s="22" t="s">
-        <v>516</v>
+        <v>497</v>
+      </c>
+      <c r="N12" s="18" t="s">
+        <v>498</v>
       </c>
       <c r="P12" s="22" t="s">
-        <v>518</v>
-      </c>
-      <c r="Q12" s="22"/>
+        <v>250</v>
+      </c>
+      <c r="Q12" s="22" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
         <v>1</v>
       </c>
       <c r="B13" s="61"/>
-      <c r="C13" s="61" t="s">
-        <v>95</v>
-      </c>
+      <c r="C13" s="61"/>
       <c r="D13" s="29" t="s">
-        <v>445</v>
+        <v>94</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>503</v>
+        <v>96</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="22" t="s">
-        <v>514</v>
-      </c>
-      <c r="I13" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="M13" s="22" t="s">
-        <v>505</v>
-      </c>
-      <c r="N13" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="P13" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q13" s="22" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
         <v>1</v>
       </c>
       <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
+      <c r="C14" s="29" t="s">
+        <v>97</v>
+      </c>
       <c r="D14" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>96</v>
+        <v>496</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="22" t="s">
-        <v>510</v>
-      </c>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26">
-        <v>1</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>445</v>
+      <c r="H14" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="I14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>498</v>
+      </c>
+      <c r="P14" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q14" s="22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="24">
+        <v>3</v>
+      </c>
+      <c r="B15" s="59" t="s">
+        <v>334</v>
+      </c>
+      <c r="C15" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>442</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>504</v>
+        <v>328</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>513</v>
-      </c>
-      <c r="I15" t="s">
-        <v>66</v>
+        <v>355</v>
+      </c>
+      <c r="H15" t="s">
+        <v>330</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>15</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>94</v>
+        <v>319</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>505</v>
-      </c>
-      <c r="N15" s="18" t="s">
-        <v>506</v>
+        <v>320</v>
+      </c>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22" t="s">
+        <v>333</v>
       </c>
       <c r="P15" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>512</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="24">
         <v>3</v>
       </c>
-      <c r="B16" s="59" t="s">
-        <v>337</v>
-      </c>
-      <c r="C16" s="59" t="s">
-        <v>61</v>
-      </c>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>445</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="E16" s="28"/>
       <c r="F16" s="22" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>15</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="N16" s="22"/>
       <c r="O16" s="22" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="P16" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="24">
-        <v>3</v>
+      <c r="A17" s="23">
+        <v>2</v>
       </c>
       <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
+      <c r="C17" s="28" t="s">
+        <v>64</v>
+      </c>
       <c r="D17" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>358</v>
+        <v>120</v>
       </c>
       <c r="H17" t="s">
-        <v>332</v>
+        <v>420</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M17" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="N17" s="22"/>
+        <v>67</v>
+      </c>
+      <c r="N17" s="22" t="s">
+        <v>68</v>
+      </c>
       <c r="O17" s="22" t="s">
-        <v>336</v>
+        <v>69</v>
       </c>
       <c r="P17" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>334</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -4173,126 +4173,122 @@
       </c>
       <c r="B18" s="59"/>
       <c r="C18" s="28" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>120</v>
+        <v>355</v>
       </c>
       <c r="H18" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="J18" s="22" t="s">
         <v>21</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="N18" s="22" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O18" s="22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="P18" s="22" t="s">
-        <v>252</v>
+        <v>348</v>
       </c>
       <c r="Q18" s="22" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="23">
-        <v>2</v>
-      </c>
-      <c r="B19" s="59"/>
-      <c r="C19" s="28" t="s">
-        <v>71</v>
+      <c r="A19" s="26">
+        <v>1</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="59" t="s">
+        <v>76</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>358</v>
+        <v>120</v>
       </c>
       <c r="H19" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I19" s="22" t="s">
         <v>46</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>282</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="K19" s="22"/>
       <c r="L19" s="22" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="N19" s="22" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="O19" s="22" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="P19" s="22" t="s">
-        <v>351</v>
+        <v>250</v>
       </c>
       <c r="Q19" s="22" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="26">
         <v>1</v>
       </c>
-      <c r="B20" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>76</v>
-      </c>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G20" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H20" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>46</v>
@@ -4302,7 +4298,7 @@
       </c>
       <c r="K20" s="22"/>
       <c r="L20" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M20" s="22" t="s">
         <v>78</v>
@@ -4314,57 +4310,59 @@
         <v>80</v>
       </c>
       <c r="P20" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q20" s="22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="26">
-        <v>1</v>
+      <c r="A21" s="23">
+        <v>2</v>
       </c>
       <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
+      <c r="C21" s="59" t="s">
+        <v>84</v>
+      </c>
       <c r="D21" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="G21" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>425</v>
+        <v>341</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>46</v>
+        <v>342</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K21" s="22"/>
+        <v>343</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>279</v>
+      </c>
       <c r="L21" s="22" t="s">
-        <v>315</v>
+        <v>489</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="N21" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="O21" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="P21" s="22" t="s">
-        <v>252</v>
+        <v>86</v>
+      </c>
+      <c r="O21" s="22"/>
+      <c r="P21" s="50" t="s">
+        <v>349</v>
       </c>
       <c r="Q21" s="22" t="s">
-        <v>83</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -4372,121 +4370,71 @@
         <v>2</v>
       </c>
       <c r="B22" s="59"/>
-      <c r="C22" s="59" t="s">
-        <v>84</v>
-      </c>
+      <c r="C22" s="59"/>
       <c r="D22" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>343</v>
+        <v>87</v>
       </c>
       <c r="G22" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H22" t="s">
-        <v>344</v>
+        <v>423</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>345</v>
+        <v>15</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>346</v>
+        <v>88</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>497</v>
+        <v>313</v>
       </c>
       <c r="M22" s="22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N22" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="O22" s="22"/>
-      <c r="P22" s="50" t="s">
-        <v>352</v>
+        <v>90</v>
+      </c>
+      <c r="O22" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="P22" s="22" t="s">
+        <v>250</v>
       </c>
       <c r="Q22" s="22" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="23">
-        <v>2</v>
-      </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="H23" t="s">
-        <v>426</v>
-      </c>
-      <c r="I23" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="K23" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="M23" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="N23" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="O23" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="P23" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q23" s="22" t="s">
         <v>91</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q23">
-    <sortCondition ref="B2:B23"/>
-    <sortCondition ref="C2:C23"/>
-    <sortCondition ref="F2:F23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q22">
+    <sortCondition ref="B2:B22"/>
+    <sortCondition ref="C2:C22"/>
+    <sortCondition ref="F2:F22"/>
   </sortState>
-  <mergeCells count="13">
-    <mergeCell ref="C22:C23"/>
+  <mergeCells count="12">
+    <mergeCell ref="C21:C22"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B19:B22"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C19:C20"/>
   </mergeCells>
-  <conditionalFormatting sqref="K2:L4 K19:L23">
+  <conditionalFormatting sqref="K2:L4 K18:L22">
     <cfRule type="cellIs" dxfId="26" priority="7" operator="equal">
       <formula>"NONE"</formula>
     </cfRule>
@@ -4497,8 +4445,8 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N13" r:id="rId1" xr:uid="{EB6BDC39-8ADC-422E-BC41-57AC7D94AB43}"/>
-    <hyperlink ref="N15" r:id="rId2" xr:uid="{BE6247DD-9AB3-4AC3-A6FB-CD722F1DEA22}"/>
+    <hyperlink ref="N12" r:id="rId1" xr:uid="{EB6BDC39-8ADC-422E-BC41-57AC7D94AB43}"/>
+    <hyperlink ref="N14" r:id="rId2" xr:uid="{BE6247DD-9AB3-4AC3-A6FB-CD722F1DEA22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4534,19 +4482,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -4558,7 +4506,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -4587,19 +4535,19 @@
         <v>99</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="I2" s="22" t="s">
         <v>15</v>
@@ -4608,10 +4556,10 @@
         <v>16</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>100</v>
@@ -4621,10 +4569,10 @@
       </c>
       <c r="O2" s="49"/>
       <c r="P2" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -4638,10 +4586,10 @@
         <v>102</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>103</v>
@@ -4657,10 +4605,10 @@
         <v>104</v>
       </c>
       <c r="K3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>105</v>
@@ -4672,7 +4620,7 @@
         <v>107</v>
       </c>
       <c r="P3" s="22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q3" s="22" t="s">
         <v>108</v>
@@ -4687,10 +4635,10 @@
         <v>109</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>110</v>
@@ -4699,7 +4647,7 @@
         <v>120</v>
       </c>
       <c r="H4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>15</v>
@@ -4708,10 +4656,10 @@
         <v>21</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>23</v>
@@ -4720,10 +4668,10 @@
         <v>24</v>
       </c>
       <c r="O4" s="22" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="P4" s="50" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="Q4" s="22" t="s">
         <v>112</v>
@@ -4738,10 +4686,10 @@
         <v>113</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>114</v>
@@ -4750,7 +4698,7 @@
         <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>15</v>
@@ -4759,10 +4707,10 @@
         <v>21</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M5" s="22" t="s">
         <v>115</v>
@@ -4772,10 +4720,10 @@
       </c>
       <c r="O5" s="22"/>
       <c r="P5" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q5" s="22" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -4787,7 +4735,7 @@
         <v>117</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="40" t="s">
@@ -4815,13 +4763,13 @@
       </c>
       <c r="B7" s="59"/>
       <c r="C7" s="47" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>119</v>
@@ -4830,7 +4778,7 @@
         <v>120</v>
       </c>
       <c r="H7" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
@@ -4839,10 +4787,10 @@
         <v>21</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>121</v>
@@ -4854,10 +4802,10 @@
         <v>123</v>
       </c>
       <c r="P7" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -4868,22 +4816,22 @@
         <v>125</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
@@ -4892,25 +4840,25 @@
         <v>94</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="N8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O8" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="P8" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -4922,7 +4870,7 @@
         <v>124</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="40" t="s">
@@ -4948,13 +4896,13 @@
       </c>
       <c r="B10" s="59"/>
       <c r="C10" s="29" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>126</v>
@@ -4963,7 +4911,7 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>15</v>
@@ -4972,10 +4920,10 @@
         <v>21</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M10" s="22" t="s">
         <v>23</v>
@@ -4987,7 +4935,7 @@
         <v>127</v>
       </c>
       <c r="P10" s="22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q10" s="22" t="s">
         <v>128</v>
@@ -5004,10 +4952,10 @@
         <v>130</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>131</v>
@@ -5016,7 +4964,7 @@
         <v>120</v>
       </c>
       <c r="H11" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>15</v>
@@ -5025,10 +4973,10 @@
         <v>21</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M11" s="22" t="s">
         <v>23</v>
@@ -5037,7 +4985,7 @@
         <v>24</v>
       </c>
       <c r="P11" s="22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q11" s="22" t="s">
         <v>132</v>
@@ -5052,10 +5000,10 @@
         <v>133</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>134</v>
@@ -5064,7 +5012,7 @@
         <v>120</v>
       </c>
       <c r="H12" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="I12" s="22" t="s">
         <v>15</v>
@@ -5073,10 +5021,10 @@
         <v>16</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="M12" s="22" t="s">
         <v>100</v>
@@ -5088,7 +5036,7 @@
         <v>135</v>
       </c>
       <c r="P12" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q12" s="22" t="s">
         <v>136</v>
@@ -5103,10 +5051,10 @@
         <v>137</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>138</v>
@@ -5115,7 +5063,7 @@
         <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I13" s="22" t="s">
         <v>15</v>
@@ -5124,10 +5072,10 @@
         <v>21</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M13" s="22" t="s">
         <v>23</v>
@@ -5139,7 +5087,7 @@
         <v>111</v>
       </c>
       <c r="P13" s="22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q13" s="22" t="s">
         <v>139</v>
@@ -5152,19 +5100,19 @@
       <c r="B14" s="59"/>
       <c r="C14" s="61"/>
       <c r="D14" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I14" s="22" t="s">
         <v>15</v>
@@ -5173,25 +5121,25 @@
         <v>94</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M14" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="N14" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O14" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="P14" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -5203,19 +5151,19 @@
         <v>140</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G15" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="I15" s="22" t="s">
         <v>46</v>
@@ -5224,23 +5172,23 @@
         <v>21</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="N15" s="22" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="O15" s="22"/>
       <c r="P15" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -5250,19 +5198,19 @@
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
       <c r="D16" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G16" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>46</v>
@@ -5271,23 +5219,23 @@
         <v>21</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="N16" s="22" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="O16" s="22"/>
       <c r="P16" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -5296,22 +5244,22 @@
       </c>
       <c r="B17" s="59"/>
       <c r="C17" s="61" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G17" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H17" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I17" s="22" t="s">
         <v>15</v>
@@ -5320,10 +5268,10 @@
         <v>21</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M17" s="22" t="s">
         <v>23</v>
@@ -5332,10 +5280,10 @@
         <v>24</v>
       </c>
       <c r="P17" s="22" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q17" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -5345,19 +5293,19 @@
       <c r="B18" s="59"/>
       <c r="C18" s="61"/>
       <c r="D18" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G18" s="22" t="s">
         <v>120</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="I18" s="22" t="s">
         <v>15</v>
@@ -5366,22 +5314,22 @@
         <v>94</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M18" t="s">
+        <v>398</v>
+      </c>
+      <c r="N18" t="s">
+        <v>399</v>
+      </c>
+      <c r="P18" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q18" s="22" t="s">
         <v>401</v>
-      </c>
-      <c r="N18" t="s">
-        <v>402</v>
-      </c>
-      <c r="P18" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q18" s="22" t="s">
-        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5450,19 +5398,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>5</v>
@@ -5474,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>8</v>
@@ -5503,19 +5451,19 @@
         <v>142</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I2" s="22" t="s">
         <v>46</v>
@@ -5524,10 +5472,10 @@
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>143</v>
@@ -5539,7 +5487,7 @@
         <v>145</v>
       </c>
       <c r="P2" s="22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q2" t="s">
         <v>146</v>
@@ -5554,19 +5502,19 @@
         <v>147</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>46</v>
@@ -5575,10 +5523,10 @@
         <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>148</v>
@@ -5590,7 +5538,7 @@
         <v>149</v>
       </c>
       <c r="P3" s="22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q3" t="s">
         <v>150</v>
@@ -5607,19 +5555,19 @@
         <v>152</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>15</v>
@@ -5628,10 +5576,10 @@
         <v>16</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>294</v>
+        <v>517</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>44</v>
@@ -5641,10 +5589,10 @@
       </c>
       <c r="O4" s="22"/>
       <c r="P4" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -5655,22 +5603,22 @@
         <v>153</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>154</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>66</v>
@@ -5678,11 +5626,11 @@
       <c r="J5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="K5" t="s">
-        <v>294</v>
+      <c r="K5" s="22" t="s">
+        <v>517</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M5" s="22" t="s">
         <v>155</v>
@@ -5692,7 +5640,7 @@
       </c>
       <c r="O5" s="22"/>
       <c r="P5" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q5" t="s">
         <v>157</v>
@@ -5706,22 +5654,22 @@
         <v>158</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>160</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I6" s="30" t="s">
         <v>15</v>
@@ -5730,10 +5678,10 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>17</v>
@@ -5743,7 +5691,7 @@
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q6" t="s">
         <v>161</v>
@@ -5758,19 +5706,19 @@
         <v>159</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>15</v>
@@ -5779,10 +5727,10 @@
         <v>16</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>294</v>
+        <v>517</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>44</v>
@@ -5791,13 +5739,13 @@
         <v>45</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="P7" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="R7"/>
     </row>
@@ -5812,19 +5760,19 @@
         <v>163</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>164</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>15</v>
@@ -5833,10 +5781,10 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M8" s="22" t="s">
         <v>17</v>
@@ -5845,13 +5793,13 @@
         <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P8" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -5863,19 +5811,19 @@
         <v>165</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>46</v>
@@ -5884,10 +5832,10 @@
         <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M9" s="22" t="s">
         <v>17</v>
@@ -5896,13 +5844,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P9" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q9" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -5912,7 +5860,7 @@
         <v>166</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="34" t="s">
@@ -5926,9 +5874,7 @@
       <c r="L10" s="34"/>
       <c r="M10" s="34"/>
       <c r="N10" s="34"/>
-      <c r="O10" s="34" t="s">
-        <v>167</v>
-      </c>
+      <c r="O10" s="34"/>
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
     </row>
@@ -5936,22 +5882,22 @@
       <c r="A11" s="24"/>
       <c r="B11" s="60"/>
       <c r="C11" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>15</v>
@@ -5960,10 +5906,10 @@
         <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M11" s="22" t="s">
         <v>44</v>
@@ -5973,10 +5919,10 @@
       </c>
       <c r="O11" s="22"/>
       <c r="P11" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q11" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -5985,22 +5931,22 @@
       </c>
       <c r="B12" s="60"/>
       <c r="C12" s="59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I12" s="22" t="s">
         <v>46</v>
@@ -6009,23 +5955,23 @@
         <v>21</v>
       </c>
       <c r="K12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="N12" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O12" s="22"/>
       <c r="P12" s="49" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q12" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -6035,19 +5981,19 @@
       <c r="B13" s="60"/>
       <c r="C13" s="59"/>
       <c r="D13" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I13" s="22" t="s">
         <v>46</v>
@@ -6056,10 +6002,10 @@
         <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M13" s="22" t="s">
         <v>44</v>
@@ -6069,10 +6015,10 @@
       </c>
       <c r="O13" s="22"/>
       <c r="P13" s="49" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q13" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -6082,19 +6028,19 @@
       <c r="B14" s="60"/>
       <c r="C14" s="59"/>
       <c r="D14" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F14" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="H14" s="22" t="s">
         <v>379</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>382</v>
       </c>
       <c r="I14" s="22" t="s">
         <v>46</v>
@@ -6103,23 +6049,23 @@
         <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="N14" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O14" s="22"/>
       <c r="P14" s="49" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q14" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -6127,13 +6073,13 @@
         <v>32</v>
       </c>
       <c r="B15" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="35" t="s">
-        <v>171</v>
-      </c>
       <c r="D15" s="35" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="44" t="s">
@@ -6148,7 +6094,7 @@
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
       <c r="O15" s="44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P15" s="35"/>
       <c r="Q15" s="35"/>
@@ -6170,12 +6116,12 @@
       <formula>"NONE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:L5">
+  <conditionalFormatting sqref="L5">
     <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"NONE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:L9">
+  <conditionalFormatting sqref="L7 K8:L9">
     <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"NONE"</formula>
     </cfRule>
@@ -6200,7 +6146,7 @@
     <col min="4" max="4" width="10.109375" style="29" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" style="29" customWidth="1"/>
     <col min="6" max="6" width="32.33203125" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" customWidth="1"/>
     <col min="8" max="8" width="47.44140625" customWidth="1"/>
     <col min="9" max="9" width="13.77734375" customWidth="1"/>
     <col min="11" max="11" width="17.5546875" customWidth="1"/>
@@ -6221,19 +6167,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I1" s="17" t="s">
         <v>5</v>
@@ -6245,7 +6191,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M1" s="17" t="s">
         <v>8</v>
@@ -6268,13 +6214,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="37" t="s">
-        <v>174</v>
-      </c>
       <c r="D2" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E2" s="37"/>
       <c r="F2" s="20" t="s">
@@ -6298,10 +6244,10 @@
       </c>
       <c r="B3" s="61"/>
       <c r="C3" s="37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E3" s="37"/>
       <c r="F3" s="20" t="s">
@@ -6325,10 +6271,10 @@
       </c>
       <c r="B4" s="61"/>
       <c r="C4" s="37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E4" s="37"/>
       <c r="F4" s="20" t="s">
@@ -6352,10 +6298,10 @@
       </c>
       <c r="B5" s="61"/>
       <c r="C5" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="20" t="s">
@@ -6379,22 +6325,22 @@
       </c>
       <c r="B6" s="61"/>
       <c r="C6" s="29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G6" t="s">
         <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
@@ -6403,25 +6349,25 @@
         <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="N6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O6" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="P6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
@@ -6430,10 +6376,10 @@
       </c>
       <c r="B7" s="61"/>
       <c r="C7" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E7" s="37"/>
       <c r="F7" t="s">
@@ -6457,10 +6403,10 @@
       </c>
       <c r="B8" s="61"/>
       <c r="C8" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E8" s="37"/>
       <c r="F8" t="s">
@@ -6483,25 +6429,25 @@
         <v>2</v>
       </c>
       <c r="B9" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>182</v>
-      </c>
       <c r="D9" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -6510,10 +6456,10 @@
         <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M9" t="s">
         <v>17</v>
@@ -6522,13 +6468,13 @@
         <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
@@ -6537,20 +6483,20 @@
       </c>
       <c r="B10" s="61"/>
       <c r="C10" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G10" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
@@ -6559,10 +6505,10 @@
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M10" t="s">
         <v>17</v>
@@ -6572,10 +6518,10 @@
       </c>
       <c r="O10"/>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
@@ -6584,20 +6530,20 @@
       </c>
       <c r="B11" s="61"/>
       <c r="C11" s="29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H11" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -6606,10 +6552,10 @@
         <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M11" t="s">
         <v>17</v>
@@ -6619,10 +6565,10 @@
       </c>
       <c r="O11"/>
       <c r="P11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
@@ -6631,10 +6577,10 @@
       </c>
       <c r="B12" s="61"/>
       <c r="C12" s="37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E12" s="37"/>
       <c r="F12" t="s">
@@ -6649,7 +6595,7 @@
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
       <c r="O12" s="20" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P12" s="20"/>
       <c r="Q12" s="20"/>
@@ -6659,10 +6605,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="61" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D13" s="29" t="s">
         <v>94</v>
@@ -6671,13 +6617,13 @@
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="G13" t="s">
         <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -6686,10 +6632,10 @@
         <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L13" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
@@ -6699,10 +6645,10 @@
       </c>
       <c r="O13"/>
       <c r="P13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q13" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
@@ -6712,11 +6658,9 @@
       <c r="D14" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>94</v>
-      </c>
+      <c r="E14" s="29"/>
       <c r="F14" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="G14" t="s">
         <v>120</v>
@@ -6730,7 +6674,7 @@
       <c r="N14"/>
       <c r="O14"/>
       <c r="P14" s="48" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="Q14"/>
     </row>
@@ -6740,34 +6684,32 @@
       </c>
       <c r="B15" s="61"/>
       <c r="C15" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" t="s">
         <v>196</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>445</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>445</v>
-      </c>
-      <c r="F15" t="s">
-        <v>197</v>
       </c>
       <c r="G15" t="s">
         <v>120</v>
       </c>
       <c r="H15" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>21</v>
+        <v>519</v>
       </c>
       <c r="K15" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L15" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M15" t="s">
         <v>23</v>
@@ -6777,10 +6719,10 @@
       </c>
       <c r="O15"/>
       <c r="P15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
@@ -6789,10 +6731,10 @@
       </c>
       <c r="B16" s="61"/>
       <c r="C16" s="37" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="20" t="s">
@@ -6807,7 +6749,7 @@
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
       <c r="O16" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
@@ -6818,10 +6760,10 @@
       </c>
       <c r="B17" s="61"/>
       <c r="C17" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E17" s="37"/>
       <c r="F17" s="20" t="s">
@@ -6836,7 +6778,7 @@
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
       <c r="O17" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P17" s="20"/>
       <c r="Q17" s="20"/>
@@ -6846,13 +6788,13 @@
         <v>32</v>
       </c>
       <c r="B18" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="C18" s="37" t="s">
-        <v>203</v>
-      </c>
       <c r="D18" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="20" t="s">
@@ -6876,10 +6818,10 @@
       </c>
       <c r="B19" s="61"/>
       <c r="C19" s="37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E19" s="37"/>
       <c r="F19" t="s">
@@ -6894,10 +6836,10 @@
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
       <c r="O19" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P19" s="57" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="Q19" s="20"/>
     </row>
@@ -6907,16 +6849,16 @@
       </c>
       <c r="B20" s="61"/>
       <c r="C20" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>520</v>
       </c>
       <c r="G20" t="s">
         <v>120</v>
@@ -6929,10 +6871,10 @@
         <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L20" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M20" t="s">
         <v>26</v>
@@ -6941,37 +6883,39 @@
         <v>27</v>
       </c>
       <c r="O20" t="s">
-        <v>208</v>
-      </c>
-      <c r="P20" s="48" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q20"/>
+        <v>206</v>
+      </c>
+      <c r="P20" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="21" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="D21" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="F21" t="s">
+        <v>437</v>
+      </c>
+      <c r="G21" t="s">
+        <v>324</v>
+      </c>
+      <c r="H21" t="s">
         <v>191</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>445</v>
-      </c>
-      <c r="E21" s="29" t="s">
-        <v>445</v>
-      </c>
-      <c r="F21" t="s">
-        <v>440</v>
-      </c>
-      <c r="G21" t="s">
-        <v>327</v>
-      </c>
-      <c r="H21" t="s">
-        <v>192</v>
       </c>
       <c r="I21" t="s">
         <v>15</v>
@@ -6980,10 +6924,10 @@
         <v>16</v>
       </c>
       <c r="K21" t="s">
-        <v>294</v>
+        <v>517</v>
       </c>
       <c r="L21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M21" t="s">
         <v>17</v>
@@ -6993,10 +6937,10 @@
       </c>
       <c r="O21"/>
       <c r="P21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.3">
@@ -7005,10 +6949,10 @@
       </c>
       <c r="B22" s="61"/>
       <c r="C22" s="37" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E22" s="37"/>
       <c r="F22" s="19" t="s">
@@ -7023,7 +6967,7 @@
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
       <c r="O22" s="20" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
@@ -7104,18 +7048,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B2" s="73"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="62" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B3" s="63"/>
     </row>
@@ -7125,13 +7069,13 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="62" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B5" s="63"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="66" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B6" s="67"/>
     </row>
@@ -7141,13 +7085,13 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="62" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B8" s="63"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="66" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B9" s="67"/>
     </row>
@@ -7157,13 +7101,13 @@
     </row>
     <row r="11" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="68" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B11" s="69"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="70" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B12" s="63"/>
     </row>
@@ -7173,19 +7117,19 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B14" s="63"/>
     </row>
     <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="64" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B15" s="65"/>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B17" s="2"/>
     </row>
@@ -7194,31 +7138,31 @@
         <v>11</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -7226,7 +7170,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -7234,7 +7178,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -7242,7 +7186,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -7250,7 +7194,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -7258,23 +7202,23 @@
         <v>7</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>314</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -7282,23 +7226,23 @@
         <v>0</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -7307,16 +7251,16 @@
     </row>
     <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -7324,25 +7268,25 @@
         <v>32</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -7377,7 +7321,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E65C56-A834-4ED4-A193-64A017DCA518}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -7411,7 +7355,7 @@
         <v>10</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H1" s="17" t="s">
         <v>8</v>
@@ -7422,10 +7366,10 @@
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C2" t="s">
         <v>38</v>
@@ -7437,21 +7381,21 @@
         <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -7460,21 +7404,21 @@
         <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -7483,7 +7427,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -7494,13 +7438,13 @@
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -7517,13 +7461,13 @@
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -7532,21 +7476,21 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -7555,21 +7499,21 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C8" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -7578,61 +7522,61 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" t="s">
+        <v>281</v>
+      </c>
+      <c r="H9" t="s">
         <v>282</v>
-      </c>
-      <c r="C9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E9" t="s">
-        <v>284</v>
-      </c>
-      <c r="H9" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D11" t="s">
         <v>66</v>
@@ -7641,21 +7585,21 @@
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C12" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -7664,21 +7608,21 @@
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H12" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -7687,7 +7631,7 @@
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -7698,13 +7642,13 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B14" t="s">
-        <v>295</v>
+        <v>517</v>
       </c>
       <c r="C14" t="s">
-        <v>299</v>
+        <v>518</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -7713,7 +7657,7 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -7724,13 +7668,13 @@
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B15" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" t="s">
         <v>296</v>
-      </c>
-      <c r="C15" t="s">
-        <v>300</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -7739,7 +7683,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -7750,13 +7694,13 @@
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B16" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" t="s">
         <v>297</v>
-      </c>
-      <c r="C16" t="s">
-        <v>301</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
@@ -7765,7 +7709,7 @@
         <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -7776,13 +7720,13 @@
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B17" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -7790,6 +7734,9 @@
       <c r="E17" t="s">
         <v>16</v>
       </c>
+      <c r="F17" t="s">
+        <v>295</v>
+      </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
@@ -7799,13 +7746,13 @@
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B18" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C18" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -7822,48 +7769,71 @@
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B19" t="s">
-        <v>499</v>
+        <v>310</v>
       </c>
       <c r="C19" t="s">
-        <v>498</v>
-      </c>
-      <c r="F19" t="s">
-        <v>500</v>
+        <v>309</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="B20" t="s">
-        <v>354</v>
+        <v>491</v>
+      </c>
+      <c r="C20" t="s">
+        <v>490</v>
       </c>
       <c r="F20" t="s">
-        <v>355</v>
-      </c>
-      <c r="G20" t="s">
-        <v>356</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B21" t="s">
-        <v>247</v>
+        <v>351</v>
       </c>
       <c r="F21" t="s">
-        <v>302</v>
+        <v>352</v>
       </c>
       <c r="G21" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.4" x14ac:dyDescent="0.3"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>283</v>
+      </c>
+      <c r="B22" t="s">
+        <v>245</v>
+      </c>
+      <c r="F22" t="s">
+        <v>299</v>
+      </c>
+      <c r="G22" t="s">
+        <v>354</v>
+      </c>
+    </row>
     <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:I7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
